--- a/资料/武器相关.xlsx
+++ b/资料/武器相关.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27195" windowHeight="13140"/>
+    <workbookView windowWidth="14355" windowHeight="12990"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
   <si>
     <t>era中没有对应武器的金属块，在原作中对应的武器</t>
   </si>
@@ -67,25 +67,43 @@
     <t>宝石の杖</t>
   </si>
   <si>
+    <t>宝石之杖</t>
+  </si>
+  <si>
     <t>梅露露</t>
   </si>
   <si>
+    <t>传说之杖</t>
+  </si>
+  <si>
     <t>サンライト</t>
   </si>
   <si>
     <t>新世界の杖</t>
   </si>
   <si>
+    <t>新世界之杖</t>
+  </si>
+  <si>
     <t>レーゲンティウム</t>
   </si>
   <si>
     <t>マスターのロッド</t>
   </si>
   <si>
+    <t>大师短杖</t>
+  </si>
+  <si>
     <t>ドライメタル</t>
   </si>
   <si>
+    <t>七星之杖</t>
+  </si>
+  <si>
     <t>無敵のロッド</t>
+  </si>
+  <si>
+    <t>无敌短杖</t>
   </si>
   <si>
     <t>era中已实装的金属块</t>
@@ -1149,11 +1167,14 @@
       <c r="A8" t="s">
         <v>16</v>
       </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -1166,42 +1187,51 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -1211,8 +1241,11 @@
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -1226,24 +1259,27 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1251,7 +1287,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1259,7 +1295,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1267,28 +1303,28 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1296,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1304,7 +1340,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
